--- a/assets_cropped/Symboli Rudolf/manifest_edit.xlsx
+++ b/assets_cropped/Symboli Rudolf/manifest_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\TanukiProject\tanuki_app\assets_cropped\Symboli Rudolf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ADCEE0-6B21-4B5E-968E-0E49875F838A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC179962-D451-4925-A1F3-946C19F62EED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="194">
   <si>
     <t>filename</t>
   </si>
@@ -86,9 +86,6 @@
     <t>low,severe</t>
   </si>
   <si>
-    <t>offer_preview,bottle_feed_hold,offer_timeout_route_a_step1,shared_food_hold</t>
-  </si>
-  <si>
     <t>idle_lie_read-happy.gif</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>idle_side_face-happy.gif</t>
   </si>
   <si>
-    <t>window_perch,relation_watch,random</t>
-  </si>
-  <si>
     <t>idle_side_face-sad.gif</t>
   </si>
   <si>
@@ -260,9 +254,6 @@
     <t>idle_sit-happy.gif</t>
   </si>
   <si>
-    <t>window_perch,care_companion,relation_watch,bottle_feed_watch,shared_food_react,random</t>
-  </si>
-  <si>
     <t>idle_sleep-happy.gif</t>
   </si>
   <si>
@@ -425,9 +416,6 @@
     <t>move_walk-sad.gif</t>
   </si>
   <si>
-    <t>window_walk,offer_timeout_route_a_step3,negative_reaction,random</t>
-  </si>
-  <si>
     <t>move_work_boxes-hurry.gif</t>
   </si>
   <si>
@@ -503,24 +491,12 @@
     <t>interaction_move_fly_Teioy-happy.gif</t>
   </si>
   <si>
-    <t>offer_preview,bottle_feed_hold,shared_food_hold,shared_food_watch</t>
-  </si>
-  <si>
     <t>relation_watch,bottle_feed_watch,shared_food_request</t>
   </si>
   <si>
     <t>offer_accept_tea,shared_food_consume</t>
   </si>
   <si>
-    <t>window_perch,relation_watch,random,shared_food_watch</t>
-  </si>
-  <si>
-    <t>window_perch,observe_hold,random,shared_food_watch</t>
-  </si>
-  <si>
-    <t>window_walk,random,shared_food_approach</t>
-  </si>
-  <si>
     <t>activity_work_stationary</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -557,14 +533,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>random,activity_sleep_settling</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>negative_reaction,random,activity_work_rest,activity_sleep_settling</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>activity_sleeping</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -573,18 +541,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>bottle_feed_watch,post_observe,activity_sleep_observing</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>idle_side_cross-sad.gif</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>activity_sleep_observing</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>window_walk,random,activity_sleep_join_approach</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -598,6 +558,86 @@
   </si>
   <si>
     <t>window_perch,care_companion,relation_watch,honey_guard_take,bottle_feed_watch,negative_reaction,random,activity_sleep_waking,activity_sleep_join_settling</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_walk,offer_timeout_route_a_step3,negative_reaction,random,activity_race_to_start</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_walk,random,shared_food_approach,activity_race_to_start</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bottle_feed_watch,post_observe,activity_sleep_observing,activity_race_ready</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_walk,random,activity_race_running</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>honey_guard_move,care_approach,activity_race_running</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,random,activity_race_finish_win</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,random,activity_race_finish_lose</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,care_companion,relation_watch,bottle_feed_watch,shared_food_react,random,activity_race_recovery</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>negative_reaction,random,activity_work_rest,activity_sleep_settling,activity_race_recovery</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>random,activity_sleep_settling,activity_race_recovery</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer_preview,bottle_feed_hold,shared_food_hold,shared_food_watch,activity_race_challenge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer_preview,bottle_feed_hold,offer_timeout_route_a_step1,shared_food_hold,activity_race_challenge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shared_food_request,relation_close</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,observe_hold,random,activity_race_accept</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,observe_hold,random,shared_food_watch,activity_race_accept</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,relation_watch,random,shared_food_watch,activity_race_accept</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,random,activity_race_decline</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>activity_sleep_observing,activity_race_decline,random,negative_reaction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,relation_watch,random,activity_race_consider</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,observe_hold,random,activity_race_ready,activity_race_consider</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1008,8 +1048,8 @@
       <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>160</v>
+      <c r="C7" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1036,8 +1076,8 @@
       <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
+      <c r="C9" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1045,13 +1085,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1059,13 +1099,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1073,13 +1113,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1087,13 +1127,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1101,13 +1141,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1115,13 +1155,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1129,13 +1169,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1143,13 +1183,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
         <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1157,13 +1197,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
         <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1171,13 +1211,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1185,13 +1225,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1199,13 +1239,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1213,13 +1253,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1227,13 +1267,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1241,13 +1281,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
-      <c r="C24" t="s">
-        <v>39</v>
+      <c r="C24" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1255,13 +1295,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
         <v>40</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" t="s">
-        <v>41</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1269,13 +1309,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1283,13 +1323,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1297,13 +1337,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1311,13 +1351,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
         <v>46</v>
-      </c>
-      <c r="B29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" t="s">
-        <v>47</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1325,13 +1365,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1339,13 +1379,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1353,13 +1393,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1367,13 +1407,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
       </c>
-      <c r="C33" t="s">
-        <v>163</v>
+      <c r="C33" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1381,13 +1421,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
         <v>20</v>
       </c>
-      <c r="C34" t="s">
-        <v>52</v>
+      <c r="C34" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1395,13 +1435,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
-      <c r="C35" t="s">
-        <v>164</v>
+      <c r="C35" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1409,13 +1449,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
-      <c r="C36" t="s">
-        <v>55</v>
+      <c r="C36" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1423,13 +1463,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
         <v>20</v>
       </c>
-      <c r="C37" t="s">
-        <v>52</v>
+      <c r="C37" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1437,13 +1477,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1451,13 +1491,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1465,13 +1505,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1479,13 +1519,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
-      <c r="C41" t="s">
-        <v>63</v>
+      <c r="C41" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1493,13 +1533,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1507,13 +1547,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1521,13 +1561,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1535,13 +1575,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1549,13 +1589,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1563,13 +1603,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1577,13 +1617,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B48" t="s">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1591,13 +1631,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1605,13 +1645,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B50" t="s">
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1619,13 +1659,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1633,13 +1673,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
       </c>
-      <c r="C52" t="s">
-        <v>79</v>
+      <c r="C52" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1647,13 +1687,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1661,7 +1701,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B54" t="s">
         <v>6</v>
@@ -1675,13 +1715,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B55" t="s">
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1689,13 +1729,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1703,13 +1743,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1717,13 +1757,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
       </c>
-      <c r="C58" t="s">
-        <v>63</v>
+      <c r="C58" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1731,13 +1771,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
       </c>
-      <c r="C59" t="s">
-        <v>63</v>
+      <c r="C59" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1745,13 +1785,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -1759,13 +1799,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
-      <c r="C61" t="s">
-        <v>63</v>
+      <c r="C61" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1773,13 +1813,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -1787,13 +1827,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -1801,13 +1841,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -1815,13 +1855,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1829,13 +1869,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1843,13 +1883,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -1857,13 +1897,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -1871,13 +1911,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B69" t="s">
         <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -1888,13 +1928,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -1905,13 +1945,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -1922,13 +1962,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s">
         <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -1939,13 +1979,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -1956,13 +1996,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -1973,13 +2013,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -1990,13 +2030,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2007,13 +2047,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2024,13 +2064,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2041,13 +2081,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2058,13 +2098,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B80" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C80" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2075,13 +2115,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2089,13 +2129,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
       </c>
       <c r="C82" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2103,13 +2143,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
         <v>20</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2117,13 +2157,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -2131,13 +2171,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2145,13 +2185,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -2159,13 +2199,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2173,13 +2213,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -2187,13 +2227,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B89" t="s">
         <v>6</v>
       </c>
-      <c r="C89" t="s">
-        <v>125</v>
+      <c r="C89" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -2201,13 +2241,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B90" t="s">
         <v>11</v>
       </c>
-      <c r="C90" t="s">
-        <v>117</v>
+      <c r="C90" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -2215,13 +2255,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -2229,13 +2269,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
-      <c r="C92" t="s">
-        <v>165</v>
+      <c r="C92" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2243,13 +2283,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B93" t="s">
         <v>20</v>
       </c>
-      <c r="C93" t="s">
-        <v>134</v>
+      <c r="C93" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -2257,13 +2297,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2271,13 +2311,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -2312,169 +2352,169 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
         <v>140</v>
       </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>141</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>142</v>
-      </c>
-      <c r="E2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" t="s">
         <v>141</v>
       </c>
-      <c r="D3" t="s">
+      <c r="H3" t="s">
         <v>142</v>
-      </c>
-      <c r="E3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" t="s">
         <v>142</v>
-      </c>
-      <c r="E4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" t="s">
+        <v>141</v>
+      </c>
+      <c r="H6" t="s">
         <v>142</v>
-      </c>
-      <c r="E6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H6" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" t="s">
         <v>142</v>
-      </c>
-      <c r="E7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/assets_cropped/Symboli Rudolf/manifest_edit.xlsx
+++ b/assets_cropped/Symboli Rudolf/manifest_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\TanukiProject\tanuki_app\assets_cropped\Symboli Rudolf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC179962-D451-4925-A1F3-946C19F62EED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2309E67E-75E2-48B3-BDE3-90178EAB0C0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="196">
   <si>
     <t>filename</t>
   </si>
@@ -561,14 +561,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>window_walk,offer_timeout_route_a_step3,negative_reaction,random,activity_race_to_start</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>window_walk,random,shared_food_approach,activity_race_to_start</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>bottle_feed_watch,post_observe,activity_sleep_observing,activity_race_ready</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -589,10 +581,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>window_perch,care_companion,relation_watch,bottle_feed_watch,shared_food_react,random,activity_race_recovery</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>negative_reaction,random,activity_work_rest,activity_sleep_settling,activity_race_recovery</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -638,6 +626,26 @@
   </si>
   <si>
     <t>window_perch,observe_hold,random,activity_race_ready,activity_race_consider</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,random,activity_race_finish_lose,activity_chorus_finish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>activity_chorus_perform</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_walk,random,shared_food_approach,activity_race_to_start,activity_chorus_approach</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_walk,offer_timeout_route_a_step3,negative_reaction,random,activity_race_to_start,activity_chorus_approach</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>window_perch,care_companion,relation_watch,bottle_feed_watch,shared_food_react,random,activity_race_recovery,activity_chorus_observe</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1049,7 +1057,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1077,7 +1085,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1133,7 +1141,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1147,7 +1155,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1216,11 +1224,11 @@
       <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C19" t="s">
-        <v>27</v>
+      <c r="C19" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,11 +1238,11 @@
       <c r="B20" t="s">
         <v>6</v>
       </c>
-      <c r="C20" t="s">
-        <v>27</v>
+      <c r="C20" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,8 +1252,8 @@
       <c r="B21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" t="s">
-        <v>27</v>
+      <c r="C21" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1258,8 +1266,8 @@
       <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" t="s">
-        <v>27</v>
+      <c r="C22" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1287,7 +1295,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1385,7 +1393,7 @@
         <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1413,7 +1421,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1427,7 +1435,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1441,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1455,7 +1463,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1469,7 +1477,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1525,7 +1533,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1609,7 +1617,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1679,7 +1687,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1763,7 +1771,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1777,7 +1785,7 @@
         <v>20</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1805,7 +1813,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2233,7 +2241,7 @@
         <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -2247,7 +2255,7 @@
         <v>11</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -2275,7 +2283,7 @@
         <v>11</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2289,7 +2297,7 @@
         <v>20</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D93">
         <v>1</v>
